--- a/pensum/ma02/MA02_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma02/MA02_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="170">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Markedsføring kapittel 2: Kjøpsatferd (V5)</t>
   </si>
@@ -191,6 +191,27 @@
     <t xml:space="preserve">e)  Hva bør Nordlys gjøre de første ukene etter montering, og hvorfor lønner det seg? To setninger, med begrepene fra kapitlet.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluering av kjøpet, etterkjøpskvaler og etterkjøpsrasjonalisering (Markedsføring 2.2.5). Påvirkerrollen (2.3) forklarer hvorfor en fornøyd kunde kan gi nye kunder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trinn og behov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Søk er å finne alternativene, vurdering er å veie dem mot hverandre, kjøp er å velge installatør, dag og betaling. For behovet: hva er far redd for?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rollene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire roller: påvirker, bruker, beslutningstager og kjøper. Spør for hver person: bestemmer hun, betaler han, eller prøver de bare å påvirke? Én person kan ha flere roller.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 2, avsnitt 2.2 (kjøpsprosessen og Maslow), 2.2.5 (etterkjøpskvaler) og 2.3 (kjøpsroller). Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -278,6 +299,21 @@
     <t xml:space="preserve">e)  Skriv to setninger Mona kan ha i tilbudet som treffer boligeierens behov, og si én ting hun gjør etter montering. Bruk begrepene fra kapitlet.</t>
   </si>
   <si>
+    <t xml:space="preserve">Flere behov samtidig og manifeste og latente behov (Markedsføring 2.2.1), søk etter alternativer (2.2.2) og evaluering med etterkjøpskvaler (2.2.5).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maslow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sikkerhet er å beskytte liv, helse og eiendom. Status er å bli sett opp til. Selvrealisering er å nå så langt som mulig, selv om det ikke lønner seg.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veblen og rasjonalitet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boka: for et Veblen-gode minker etterspørselen når prisen settes ned. Og: fullkommen rasjonalitet i kjøpsprosessen har bare teoretisk interesse.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 2, avsnitt 2.2.1 (behov, Maslow, Freud og Veblen) og 2.2.2 (søk etter alternativer). Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -347,6 +383,9 @@
     <t xml:space="preserve">a)  Hva koster anlegget per leilighet, i kroner? Laget er ikke mva-registrert, så bruk prisen inkl. mva og del på antall leiligheter.</t>
   </si>
   <si>
+    <t xml:space="preserve">Pris per enhet = totalpris / antall enheter. Pris uten mva = pris inkl. mva / 1,25 (mva 25 %, merverdiavgiftsloven § 5-1). Regnestykket står ikke i Markedsføring kap. 2, men det handler om «riktig pris», ett av de fire kravene i 2.4.</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Borettslaget har aldri hatt ladeanlegg. Hvilken kjøpssituasjon er det?   A: Nyanskaffelse   B: Overveid gjenkjøp   C: Rent gjenkjøp   (skriv bokstaven)</t>
   </si>
   <si>
@@ -374,6 +413,21 @@
     <t xml:space="preserve">e)  Les Idas brev i situasjonen. Finn minst tre feil om kjøpsatferd, sett navn på begrepet for hver, og si hva brevet burde inneholdt.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formalisert kjøpsatferd og de fire «riktig» (Markedsføring 2.4), tabell 2.1 trinn 6 og 7, og kjøpsrollene med portvakten (2.5).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pris og situasjon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laget får ikke fradrag for mva, så del hele 1 350 000 på 48. Har borettslaget kjøpt et slikt anlegg før? Da vet du situasjonen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rollene og valget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spør for hver person: tok hun initiativet, gir han råd, vedtar de, eller sorterer hun posten? Og trinn 6 i tabell 2.1: hva avgjør valget av leverandør?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 2, avsnitt 2.4 (formalisert kjøpsatferd, kjøpssituasjoner, tabell 2.1) og 2.5 (kjøpsroller og portvakten). Merverdiavgift 25 %: merverdiavgiftsloven § 5-1. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -437,6 +491,9 @@
     <t xml:space="preserve">b)  Prosjektet er anslått til 1 800 fakturerbare timer. Fjell har 3 500 fakturerbare timer i et år. Hvor stor andel av årskapasiteten binder prosjektet? Svar i prosent med én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Andel i prosent = del / helhet × 100. Ingen formel i Markedsføring kap. 2; tallet belyser kravet om riktig tidspunkt (2.4).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Ja eller nei for hver påstand om det Haugerud Bygg kjøper (avsnitt 2.4).</t>
   </si>
   <si>
@@ -459,6 +516,21 @@
   </si>
   <si>
     <t xml:space="preserve">e)  Hva skal stå i Fjell Elektros tilbud for å redusere kjøpsrisikoen for Haugerud Bygg? Og er det at prosjektet binder 51,4 % av årskapasiteten et argument for eller mot Fjell? To–tre setninger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formalisert kjøpsatferd og de fire «riktig», produktkategoriene (Markedsføring 2.4), portvakten og eksterne konsulenter (2.5).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Situasjon og kapasitet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rent gjenkjøp er når bestillingene går automatisk på en avtale. Hva skjer når avtalen utløper? Kapasitet: 1 800 delt på 3 500, ganger 100.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varer og portvakt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inngår det i rekkehusene? Da er det produksjon. Holder det bare virksomheten i gang? Da er det institusjonsvare. Portvakten: boka sier hva leverandøren skal gjøre med ham.</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 2, avsnitt 2.4 (kjøpssituasjoner, produktkategorier, de fire «riktig») og 2.5 (portvakten, eksterne konsulenter). Haugerud Bygg AS og Fjell Elektro AS er konstruerte casebedrifter.</t>
@@ -472,7 +544,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -539,8 +611,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -557,6 +651,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFFBF6EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -609,7 +721,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -662,6 +774,26 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -695,8 +827,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -724,7 +856,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1027,7 +1159,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1357,30 +1489,80 @@
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
     </row>
-    <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="B31" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+    </row>
+    <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="29">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1404,8 +1586,12 @@
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A28:G30"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A39:G39"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1422,7 +1608,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1433,7 +1619,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1443,7 +1629,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1454,7 +1640,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1478,10 +1664,10 @@
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1491,10 +1677,10 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1504,10 +1690,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1517,10 +1703,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1530,10 +1716,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1543,10 +1729,10 @@
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1556,10 +1742,10 @@
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1584,7 +1770,7 @@
     </row>
     <row r="17" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1598,7 +1784,7 @@
     </row>
     <row r="18" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1612,7 +1798,7 @@
     </row>
     <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1621,7 +1807,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1635,7 +1821,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -1649,7 +1835,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1663,7 +1849,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -1677,7 +1863,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -1691,7 +1877,7 @@
     </row>
     <row r="25" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1705,7 +1891,7 @@
     </row>
     <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -1739,30 +1925,80 @@
       <c r="F29" s="12"/>
       <c r="G29" s="12"/>
     </row>
-    <row r="31" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+    </row>
+    <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="28">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1785,8 +2021,12 @@
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A27:G29"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1803,7 +2043,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1814,7 +2054,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1824,7 +2064,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1835,7 +2075,7 @@
     </row>
     <row r="5" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1859,10 +2099,10 @@
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1872,10 +2112,10 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1885,10 +2125,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1898,10 +2138,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1911,10 +2151,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1924,10 +2164,10 @@
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1937,10 +2177,10 @@
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1950,10 +2190,10 @@
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -1963,10 +2203,10 @@
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
@@ -1991,44 +2231,34 @@
     </row>
     <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="13"/>
+      <c r="F19" s="18"/>
       <c r="G19" s="11" t="str">
         <f aca="false">IF(F19="","",IF(ABS(F19-(28125))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="11" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="A","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+    </row>
+    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -2036,27 +2266,22 @@
       <c r="E22" s="7"/>
       <c r="F22" s="10"/>
       <c r="G22" s="11" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="A","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="11" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -2070,7 +2295,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -2078,13 +2303,13 @@
       <c r="E25" s="7"/>
       <c r="F25" s="10"/>
       <c r="G25" s="11" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -2092,13 +2317,13 @@
       <c r="E26" s="7"/>
       <c r="F26" s="10"/>
       <c r="G26" s="11" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -2106,36 +2331,46 @@
       <c r="E27" s="7"/>
       <c r="F27" s="10"/>
       <c r="G27" s="11" t="str">
-        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="11" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="11" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12"/>
@@ -2146,30 +2381,98 @@
       <c r="F31" s="12"/>
       <c r="G31" s="12"/>
     </row>
-    <row r="33" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+    </row>
+    <row r="41" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="31">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2184,8 +2487,7 @@
     <mergeCell ref="B16:G16"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
@@ -2193,9 +2495,15 @@
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A29:G31"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2212,7 +2520,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2223,7 +2531,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2233,7 +2541,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2244,7 +2552,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2268,10 +2576,10 @@
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2281,10 +2589,10 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2294,10 +2602,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2307,10 +2615,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2320,10 +2628,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2333,10 +2641,10 @@
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2346,10 +2654,10 @@
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -2359,10 +2667,10 @@
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -2387,7 +2695,7 @@
     </row>
     <row r="18" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -2401,58 +2709,43 @@
     </row>
     <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="13"/>
+      <c r="F19" s="18"/>
       <c r="G19" s="11" t="str">
         <f aca="false">IF(F19="","",IF(ABS(F19-(51.4))&lt;=0.1,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="11" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+    </row>
+    <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="11" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -2460,13 +2753,13 @@
       <c r="E23" s="7"/>
       <c r="F23" s="10"/>
       <c r="G23" s="11" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="JA","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -2478,9 +2771,9 @@
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -2488,13 +2781,13 @@
       <c r="E25" s="7"/>
       <c r="F25" s="10"/>
       <c r="G25" s="11" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -2502,36 +2795,46 @@
       <c r="E26" s="7"/>
       <c r="F26" s="10"/>
       <c r="G26" s="11" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="11" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="11" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12"/>
@@ -2542,30 +2845,98 @@
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
     </row>
-    <row r="32" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+    </row>
+    <row r="40" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="30">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2580,17 +2951,22 @@
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:G30"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ma02/MA02_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma02/MA02_Klasseoppgaver_v5.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Kort oppsummert: Forbrukeren går gjennom fem trinn: behov, søk etter alternativer, vurdering av alternativer, kjøp og evaluering. Et behov er en følt mangeltilstand som søkes fjernet; Maslow ordner behovene i fem nivåer. Ved større kjøp har familien fire kjøpsroller: påvirker, bruker, beslutningstager og kjøper. Etter kjøpet kommer ofte etterkjøpskvalene, og selgeren kan dempe dem ved å være tilgjengelig.</t>
   </si>
   <si>
-    <t xml:space="preserve">Familien Lunde bor i en enebolig i Oslo og har bestilt elbil med levering i mars. De har fått tre tilbud på ladeboks: Nordlys 19 900 kr, tilbud B 17 500 kr og tilbud C 18 900 kr, alle inkl. mva og montering. Datteren på 17 har funnet et bestemt merke og mast om det i ukevis. Naboen har ladeboks fra Nordlys og anbefalte dem. Far sier at han først og fremst vil slippe å dra skjøteledning ut av kjellervinduet hele vinteren. Mor og far bestemmer sammen; far ringer, bestiller og betaler. Nordlys fikk jobben. To uker etter montering sier mor: «Burde vi ikke tatt den billigste?» Bruk læreboka kap. 2.2–2.3 og svar på deloppgavene.</t>
+    <t xml:space="preserve">Familien Lunde bor i en enebolig i Oslo og har bestilt elbil med levering i mars. De har fått tre tilbud på ladeboks: Nordlys 19 900 kr, tilbud B 17 500 kr og tilbud C 18 900 kr, alle inkludert merverdiavgift og montering. Datteren på 17 har funnet et bestemt merke og mast om det i ukevis. Naboen har ladeboks fra Nordlys og anbefalte dem. Far sier at han først og fremst vil slippe å dra skjøteledning ut av kjellervinduet hele vinteren. Mor og far bestemmer sammen; far ringer, bestiller og betaler. Nordlys fikk jobben. To uker etter montering sier mor: «Burde vi ikke tatt den billigste?» Bruk læreboka kap. 2.2–2.3 og svar på deloppgavene.</t>
   </si>
   <si>
     <t xml:space="preserve">Forutsetning</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">Kort oppsummert: Et borettslag kjøper som en bedrift: formalisert, etter regler som skal sikre riktig vare, mengde, pris og tidspunkt og redusere kjøpsrisikoen. En nyanskaffelse går gjennom alle åtte trinnene i tabell 2.1, og leverandøren velges etter tekniske, økonomiske og tidsplanmessige krav. Kjøpsrollene er initiativtager, påvirker, bruker, beslutningstager, godkjenner, innkjøper og portvakt.</t>
   </si>
   <si>
-    <t xml:space="preserve">Borettslaget har 48 leiligheter og 52 parkeringsplasser og har aldri hatt ladeanlegg. Styrelederen tok initiativet etter klager fra beboere. En beboer som er elektroingeniør, er den eneste i styret som forstår lastbalansering, og styret stoler på ham. En innleid rådgiver skrev kravspesifikasjonen. Forretningsføreren sorterer henvendelsene fra leverandører og sender ut forespørslene. Styret på fem innstiller på leverandør, og generalforsamlingen i mai vedtar låneopptaket. Anlegget koster 1 350 000 kr inkl. mva. Laget er ikke mva-registrert, så hele summen må lånes. Nordlys leverte det billigste av tre anbud og tapte. Ida sendte dette til styret: «Hei! Vedlagt følger vårt tilbud, 1 350 000 kr inkl. mva. Vi bruker markedets beste lader med dynamisk lastbalansering. Prisen er den laveste du får i byen. Ring meg gjerne direkte hvis du lurer på noe teknisk. Vi kan starte om tre uker.»</t>
+    <t xml:space="preserve">Borettslaget har 48 leiligheter og 52 parkeringsplasser og har aldri hatt ladeanlegg. Styrelederen tok initiativet etter klager fra beboere. En beboer som er elektroingeniør, er den eneste i styret som forstår lastbalansering, og styret stoler på ham. En innleid rådgiver skrev kravspesifikasjonen. Forretningsføreren sorterer henvendelsene fra leverandører og sender ut forespørslene. Styret på fem innstiller på leverandør, og generalforsamlingen i mai vedtar låneopptaket. Anlegget koster 1 350 000 kr inkludert merverdiavgift (mva). Laget er ikke mva-registrert, så hele summen må lånes. Nordlys leverte det billigste av tre anbud og tapte. Ida sendte dette til styret: «Hei! Vedlagt følger vårt tilbud, 1 350 000 kr inkludert mva. Vi bruker markedets beste lader med dynamisk lastbalansering. Prisen er den laveste du får i byen. Ring meg gjerne direkte hvis du lurer på noe teknisk. Vi kan starte om tre uker.»</t>
   </si>
   <si>
     <t xml:space="preserve">Borettslaget</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">Anlegget</t>
   </si>
   <si>
-    <t xml:space="preserve">Lading på alle plasser, 1 350 000 kr inkl. mva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laget er ikke mva-registrert: alt lånes</t>
+    <t xml:space="preserve">Lading på alle plasser, 1 350 000 kr inkludert merverdiavgift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merverdiavgift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laget er ikke registrert for merverdiavgift: alt lånes</t>
   </si>
   <si>
     <t xml:space="preserve">Styrelederen</t>
@@ -380,10 +380,10 @@
     <t xml:space="preserve">Billigst av tre anbud, men tapte</t>
   </si>
   <si>
-    <t xml:space="preserve">a)  Hva koster anlegget per leilighet, i kroner? Laget er ikke mva-registrert, så bruk prisen inkl. mva og del på antall leiligheter.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pris per enhet = totalpris / antall enheter. Pris uten mva = pris inkl. mva / 1,25 (mva 25 %, merverdiavgiftsloven § 5-1). Regnestykket står ikke i Markedsføring kap. 2, men det handler om «riktig pris», ett av de fire kravene i 2.4.</t>
+    <t xml:space="preserve">a)  Hva koster anlegget per leilighet, i kroner? Laget er ikke registrert for merverdiavgift, så bruk prisen inkludert merverdiavgift og del på antall leiligheter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pris per enhet = totalpris / antall enheter. Pris uten merverdiavgift = pris med merverdiavgift / 1,25 (merverdiavgift 25 %, merverdiavgiftsloven § 5-1). Regnestykket står ikke i Markedsføring kap. 2, men det handler om «riktig pris», ett av de fire kravene i 2.4.</t>
   </si>
   <si>
     <t xml:space="preserve">b)  Borettslaget har aldri hatt ladeanlegg. Hvilken kjøpssituasjon er det?   A: Nyanskaffelse   B: Overveid gjenkjøp   C: Rent gjenkjøp   (skriv bokstaven)</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">Pris og situasjon</t>
   </si>
   <si>
-    <t xml:space="preserve">Laget får ikke fradrag for mva, så del hele 1 350 000 på 48. Har borettslaget kjøpt et slikt anlegg før? Da vet du situasjonen.</t>
+    <t xml:space="preserve">Laget får ikke fradrag for merverdiavgift, så del hele 1 350 000 på 48. Har borettslaget kjøpt et slikt anlegg før? Da vet du situasjonen.</t>
   </si>
   <si>
     <t xml:space="preserve">Rollene og valget</t>

--- a/pensum/ma02/MA02_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma02/MA02_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="170">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Markedsføring kapittel 2: Kjøpsatferd (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Markedsføring kapittel 2: Kjøpsatferd (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>

--- a/pensum/ma02/MA02_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma02/MA02_Klasseoppgaver_v5.xlsx
@@ -437,7 +437,7 @@
     <t xml:space="preserve">Kort oppsummert: Kjøpssituasjonen avgjør hvor lett en ny leverandør kommer inn: ved et rent gjenkjøp nærmest ikke, ved et overveid gjenkjøp sjekkes markedet på nytt. Produksjonsvarer påvirker kvaliteten på egen leveranse mest direkte, så kjøpsprosessen bør være grundigst der. Portvakten skiller interessante henvendelser fra mindre interessante; leverandøren må bygge en god relasjon til henne eller ham.</t>
   </si>
   <si>
-    <t xml:space="preserve">Haugerud Bygg AS er en byggentreprenør i Oslo øst som skal bygge 24 rekkehus. Elektroarbeidet er anslått til om lag 1 800 fakturerbare timer over seks måneder. I fire år har Haugerud kjøpt elektro fra samme installatør på rammeavtale, men avtalen utløper nå, og innkjøpssjefen henter inn nye priser. Innkjøpssjefen sorterer alle henvendelser fra leverandører. En rådgivende ingeniør er leid inn av byggherren og gir råd om elektroanlegget. Fjell Elektro har 3 500 fakturerbare timer i året og tre årsverk. Mona vil ringe daglig leder i Haugerud direkte for å slippe innkjøpssjefen. Bruk læreboka kap. 2.4–2.5 og svar på deloppgavene.</t>
+    <t xml:space="preserve">Haugerud Bygg AS er en byggentreprenør i Oslo øst som skal bygge 24 rekkehus. Elektroarbeidet er anslått til om lag 1 800 fakturerbare timer over seks måneder. I fire år har Haugerud kjøpt elektro fra samme installatør på rammeavtale, men avtalen utløper nå, og innkjøpssjefen henter inn nye priser. Innkjøpssjefen sorterer alle henvendelser fra leverandører. En rådgivende ingeniør er leid inn av byggherren og gir råd om elektroanlegget. Fjell Elektro har 3 500 fakturerbare timer i året (to montører à 1 400 timer og Mona 700) og tre årsverk. Mona vil ringe daglig leder i Haugerud direkte for å slippe innkjøpssjefen. Bruk læreboka kap. 2.4–2.5 og svar på deloppgavene.</t>
   </si>
   <si>
     <t xml:space="preserve">Haugerud Bygg AS</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">Leid inn av byggherren, gir råd om elektro</t>
   </si>
   <si>
-    <t xml:space="preserve">3 500 fakturerbare timer i året, 3 årsverk</t>
+    <t xml:space="preserve">3 årsverk, 3 500 timer i året (2 × 1 400 + 700)</t>
   </si>
   <si>
     <t xml:space="preserve">Mona vil</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">d)  Mona vil ringe daglig leder i Haugerud direkte for å slippe innkjøpssjefen. Hva sier læreboka?   A: Lurt: den som bestemmer, bør høre det først   B: Ikke lurt: hun må bygge en god relasjon med portvakten, ellers blir henvendelsen stengt ute   C: Det spiller ingen rolle hvem hun kontakter   (skriv bokstaven)</t>
   </si>
   <si>
-    <t xml:space="preserve">e)  Hva skal stå i Fjell Elektros tilbud for å redusere kjøpsrisikoen for Haugerud Bygg? Og er det at prosjektet binder 51,4 % av årskapasiteten et argument for eller mot Fjell? To–tre setninger.</t>
+    <t xml:space="preserve">e)  Hva skal stå i Fjell Elektros tilbud for å redusere kjøpsrisikoen for Haugerud Bygg? Og er det at prosjektet binder 51,4 % av årskapasiteten (1 800 / 3 500, fra b) et argument for eller mot Fjell? To–tre setninger.</t>
   </si>
   <si>
     <t xml:space="preserve">Formalisert kjøpsatferd og de fire «riktig», produktkategoriene (Markedsføring 2.4), portvakten og eksterne konsulenter (2.5).</t>
@@ -2550,7 +2550,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>137</v>
       </c>
